--- a/research/traditional_assets/database/data/spain/spain_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.008630000000000001</v>
+        <v>0.00664</v>
       </c>
       <c r="E2">
-        <v>0.0576</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="F2">
-        <v>0.233</v>
+        <v>0.06365</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>20604.8</v>
+        <v>15468.7</v>
       </c>
       <c r="L2">
-        <v>0.2549389093383649</v>
+        <v>0.2524080313945614</v>
       </c>
       <c r="M2">
-        <v>3266.4321</v>
+        <v>3823.3178</v>
       </c>
       <c r="N2">
-        <v>0.02618625940368002</v>
+        <v>0.04481723286261372</v>
       </c>
       <c r="O2">
-        <v>0.1585277265491536</v>
+        <v>0.2471647779063528</v>
       </c>
       <c r="P2">
-        <v>2329.9321</v>
+        <v>3823.3178</v>
       </c>
       <c r="Q2">
-        <v>0.0186785472637135</v>
+        <v>0.04481723286261372</v>
       </c>
       <c r="R2">
-        <v>0.1130771519257649</v>
+        <v>0.2471647779063528</v>
       </c>
       <c r="S2">
-        <v>936.5</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.2867042605906304</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>446889.1</v>
+        <v>328112.4</v>
       </c>
       <c r="V2">
-        <v>3.58261048722767</v>
+        <v>3.846159436683777</v>
       </c>
       <c r="W2">
-        <v>0.1060109894016662</v>
+        <v>0.1057266777314806</v>
       </c>
       <c r="X2">
-        <v>0.1261788681624226</v>
+        <v>0.2069635545364273</v>
       </c>
       <c r="Y2">
-        <v>-0.02016787876075639</v>
+        <v>-0.1012368768049466</v>
       </c>
       <c r="Z2">
-        <v>0.1609047416455853</v>
+        <v>0.1612331218180962</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05316587353156453</v>
+        <v>0.08107180266822825</v>
       </c>
       <c r="AC2">
-        <v>-0.05316587353156453</v>
+        <v>-0.08107180266822825</v>
       </c>
       <c r="AD2">
-        <v>585750</v>
+        <v>425192.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>585750</v>
+        <v>425192.2</v>
       </c>
       <c r="AG2">
-        <v>138860.9</v>
+        <v>97079.79999999999</v>
       </c>
       <c r="AH2">
-        <v>0.8244328830702936</v>
+        <v>0.8328915127150508</v>
       </c>
       <c r="AI2">
-        <v>0.7162587120353842</v>
+        <v>0.7439891850124375</v>
       </c>
       <c r="AJ2">
-        <v>0.5267878177218225</v>
+        <v>0.5322681369315786</v>
       </c>
       <c r="AK2">
-        <v>0.3743870348501761</v>
+        <v>0.3988638847483142</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unicaja Banco, S.A. (BME:UNI)</t>
+          <t>Banco Bilbao Vizcaya Argentaria, S.A. (BME:BBVA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.053</v>
+        <v>-0.00282</v>
       </c>
       <c r="E3">
-        <v>0.529</v>
+        <v>0.0842</v>
       </c>
       <c r="F3">
-        <v>0.498</v>
+        <v>0.0673</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1617.8</v>
+        <v>6063.9</v>
       </c>
       <c r="L3">
-        <v>1.822257265149809</v>
+        <v>0.2892681833143315</v>
       </c>
       <c r="M3">
-        <v>37.1644</v>
+        <v>2035.8422</v>
       </c>
       <c r="N3">
-        <v>0.01422887553122248</v>
+        <v>0.05696527814697397</v>
       </c>
       <c r="O3">
-        <v>0.02297218444801583</v>
+        <v>0.3357314929335906</v>
       </c>
       <c r="P3">
-        <v>37.1644</v>
+        <v>2035.8422</v>
       </c>
       <c r="Q3">
-        <v>0.01422887553122248</v>
+        <v>0.05696527814697397</v>
       </c>
       <c r="R3">
-        <v>0.02297218444801583</v>
+        <v>0.3357314929335906</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>17810.6</v>
+        <v>86366</v>
       </c>
       <c r="V3">
-        <v>6.819020636318388</v>
+        <v>2.416623062652672</v>
       </c>
       <c r="W3">
-        <v>0.3380911579695304</v>
+        <v>0.1164229309341827</v>
       </c>
       <c r="X3">
-        <v>0.08096947608768752</v>
+        <v>0.1206119787453681</v>
       </c>
       <c r="Y3">
-        <v>0.2571216818818429</v>
+        <v>-0.004189047811185356</v>
       </c>
       <c r="Z3">
-        <v>2.363055629491617</v>
+        <v>0.1285951512348273</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05253611673052132</v>
+        <v>0.08085456885908493</v>
       </c>
       <c r="AC3">
-        <v>-0.05253611673052132</v>
+        <v>-0.08085456885908493</v>
       </c>
       <c r="AD3">
-        <v>3474.7</v>
+        <v>53746.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3474.7</v>
+        <v>53746.8</v>
       </c>
       <c r="AG3">
-        <v>-14335.9</v>
+        <v>-32619.2</v>
       </c>
       <c r="AH3">
-        <v>0.5708770085104984</v>
+        <v>0.6006228969962597</v>
       </c>
       <c r="AI3">
-        <v>0.3327013854977547</v>
+        <v>0.5234704014648305</v>
       </c>
       <c r="AJ3">
-        <v>1.222782326850904</v>
+        <v>-10.45788849347566</v>
       </c>
       <c r="AK3">
-        <v>1.946040968140416</v>
+        <v>-2.000196222712779</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0178</v>
+        <v>0.0161</v>
       </c>
       <c r="E4">
-        <v>0.0576</v>
+        <v>0.07519999999999999</v>
       </c>
       <c r="F4">
-        <v>0.187</v>
+        <v>0.06</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,28 +859,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>7100.1</v>
+        <v>9404.799999999999</v>
       </c>
       <c r="L4">
-        <v>0.1669292042056163</v>
+        <v>0.2332447125114083</v>
       </c>
       <c r="M4">
-        <v>1587.6123</v>
+        <v>1787.4756</v>
       </c>
       <c r="N4">
-        <v>0.02793326577040215</v>
+        <v>0.03605904282359776</v>
       </c>
       <c r="O4">
-        <v>0.2236042168420163</v>
+        <v>0.190059926845866</v>
       </c>
       <c r="P4">
-        <v>1587.6123</v>
+        <v>1787.4756</v>
       </c>
       <c r="Q4">
-        <v>0.02793326577040215</v>
+        <v>0.03605904282359776</v>
       </c>
       <c r="R4">
-        <v>0.2236042168420163</v>
+        <v>0.190059926845866</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,432 +889,60 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>221412.8</v>
+        <v>241746.4</v>
       </c>
       <c r="V4">
-        <v>3.895650460360441</v>
+        <v>4.876790368523404</v>
       </c>
       <c r="W4">
-        <v>0.07396623228611819</v>
+        <v>0.09503042452877851</v>
       </c>
       <c r="X4">
-        <v>0.2021756120562327</v>
+        <v>0.2933151303274865</v>
       </c>
       <c r="Y4">
-        <v>-0.1282093797701145</v>
+        <v>-0.1982847057987079</v>
       </c>
       <c r="Z4">
-        <v>0.1477365877786021</v>
+        <v>0.1857419247848758</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0531584244126477</v>
+        <v>0.08128903647737157</v>
       </c>
       <c r="AC4">
-        <v>-0.0531584244126477</v>
+        <v>-0.08128903647737157</v>
       </c>
       <c r="AD4">
-        <v>354186.4</v>
+        <v>371445.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>354186.4</v>
+        <v>371445.4</v>
       </c>
       <c r="AG4">
-        <v>132773.6</v>
+        <v>129699</v>
       </c>
       <c r="AH4">
-        <v>0.8617206414347834</v>
+        <v>0.8822591624740331</v>
       </c>
       <c r="AI4">
-        <v>0.7616644835890699</v>
+        <v>0.7922829891994783</v>
       </c>
       <c r="AJ4">
-        <v>0.7002476141754501</v>
+        <v>0.723484937228691</v>
       </c>
       <c r="AK4">
-        <v>0.5450397880161821</v>
+        <v>0.5711529010563547</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Banco Bilbao Vizcaya Argentaria, S.A. (BME:BBVA)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>-0.027</v>
-      </c>
-      <c r="E5">
-        <v>0.0438</v>
-      </c>
-      <c r="F5">
-        <v>0.233</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>5367.4</v>
-      </c>
-      <c r="L5">
-        <v>0.2609156401606113</v>
-      </c>
-      <c r="M5">
-        <v>1392</v>
-      </c>
-      <c r="N5">
-        <v>0.0352041435681625</v>
-      </c>
-      <c r="O5">
-        <v>0.2593434437530275</v>
-      </c>
-      <c r="P5">
-        <v>455.5</v>
-      </c>
-      <c r="Q5">
-        <v>0.01151974669202444</v>
-      </c>
-      <c r="R5">
-        <v>0.08486418004993107</v>
-      </c>
-      <c r="S5">
-        <v>936.5</v>
-      </c>
-      <c r="T5">
-        <v>0.6727729885057471</v>
-      </c>
-      <c r="U5">
-        <v>12940.4</v>
-      </c>
-      <c r="V5">
-        <v>0.3272670254521911</v>
-      </c>
-      <c r="W5">
-        <v>0.1060109894016662</v>
-      </c>
-      <c r="X5">
-        <v>0.1261788681624226</v>
-      </c>
-      <c r="Y5">
-        <v>-0.02016787876075639</v>
-      </c>
-      <c r="Z5">
-        <v>0.1109362065850745</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.05316587353156453</v>
-      </c>
-      <c r="AC5">
-        <v>-0.05316587353156453</v>
-      </c>
-      <c r="AD5">
-        <v>124891.1</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>124891.1</v>
-      </c>
-      <c r="AG5">
-        <v>111950.7</v>
-      </c>
-      <c r="AH5">
-        <v>0.7595308452921847</v>
-      </c>
-      <c r="AI5">
-        <v>0.6806087877270243</v>
-      </c>
-      <c r="AJ5">
-        <v>0.7389899763353061</v>
-      </c>
-      <c r="AK5">
-        <v>0.6563763677842291</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CaixaBank, S.A. (BME:CABK)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.0876</v>
-      </c>
-      <c r="E6">
-        <v>0.472</v>
-      </c>
-      <c r="F6">
-        <v>0.163</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>6323.6</v>
-      </c>
-      <c r="L6">
-        <v>0.5266901543356405</v>
-      </c>
-      <c r="M6">
-        <v>249.6554</v>
-      </c>
-      <c r="N6">
-        <v>0.01134183782408606</v>
-      </c>
-      <c r="O6">
-        <v>0.03947994813081156</v>
-      </c>
-      <c r="P6">
-        <v>249.6554</v>
-      </c>
-      <c r="Q6">
-        <v>0.01134183782408606</v>
-      </c>
-      <c r="R6">
-        <v>0.03947994813081156</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>135897.1</v>
-      </c>
-      <c r="V6">
-        <v>6.173801443764509</v>
-      </c>
-      <c r="W6">
-        <v>0.219570206840996</v>
-      </c>
-      <c r="X6">
-        <v>0.125508952580163</v>
-      </c>
-      <c r="Y6">
-        <v>0.094061254260833</v>
-      </c>
-      <c r="Z6">
-        <v>1.049969829207076</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.05399907183764642</v>
-      </c>
-      <c r="AC6">
-        <v>-0.05399907183764642</v>
-      </c>
-      <c r="AD6">
-        <v>68929.10000000001</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>68929.10000000001</v>
-      </c>
-      <c r="AG6">
-        <v>-66968</v>
-      </c>
-      <c r="AH6">
-        <v>0.757954058125598</v>
-      </c>
-      <c r="AI6">
-        <v>0.6286948733290526</v>
-      </c>
-      <c r="AJ6">
-        <v>1.489630995571235</v>
-      </c>
-      <c r="AK6">
-        <v>2.5503166569556</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Banco de Sabadell, S.A. (BME:SAB)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>-0.008630000000000001</v>
-      </c>
-      <c r="E7">
-        <v>-0.263</v>
-      </c>
-      <c r="F7">
-        <v>3.192</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>195.9</v>
-      </c>
-      <c r="L7">
-        <v>0.04061450429157856</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>-0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>-0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>58828.2</v>
-      </c>
-      <c r="V7">
-        <v>15.73830225527703</v>
-      </c>
-      <c r="W7">
-        <v>0.0131765687111984</v>
-      </c>
-      <c r="X7">
-        <v>0.274783626117696</v>
-      </c>
-      <c r="Y7">
-        <v>-0.2616070574064976</v>
-      </c>
-      <c r="Z7">
-        <v>0.2811887883592948</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.05825787882344392</v>
-      </c>
-      <c r="AC7">
-        <v>-0.05825787882344392</v>
-      </c>
-      <c r="AD7">
-        <v>34268.7</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>34268.7</v>
-      </c>
-      <c r="AG7">
-        <v>-24559.5</v>
-      </c>
-      <c r="AH7">
-        <v>0.901651292143996</v>
-      </c>
-      <c r="AI7">
-        <v>0.6966117405993487</v>
-      </c>
-      <c r="AJ7">
-        <v>1.179520305836247</v>
-      </c>
-      <c r="AK7">
-        <v>2.549040976460331</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/spain/spain_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00664</v>
+        <v>0.03075</v>
       </c>
       <c r="E2">
-        <v>0.07969999999999999</v>
+        <v>0.09475</v>
       </c>
       <c r="F2">
-        <v>0.06365</v>
+        <v>0.08079999999999998</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>15468.7</v>
+        <v>19070.7</v>
       </c>
       <c r="L2">
-        <v>0.2524080313945614</v>
+        <v>0.260797680667902</v>
       </c>
       <c r="M2">
-        <v>3823.3178</v>
+        <v>6037.967</v>
       </c>
       <c r="N2">
-        <v>0.04481723286261372</v>
+        <v>0.05057567630050056</v>
       </c>
       <c r="O2">
-        <v>0.2471647779063528</v>
+        <v>0.3166096157980567</v>
       </c>
       <c r="P2">
-        <v>3823.3178</v>
+        <v>5096.267</v>
       </c>
       <c r="Q2">
-        <v>0.04481723286261372</v>
+        <v>0.04268773746741628</v>
       </c>
       <c r="R2">
-        <v>0.2471647779063528</v>
+        <v>0.2672302013035704</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>941.6999999999998</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1559630915505169</v>
       </c>
       <c r="U2">
-        <v>328112.4</v>
+        <v>243697.1</v>
       </c>
       <c r="V2">
-        <v>3.846159436683777</v>
+        <v>2.041274098545208</v>
       </c>
       <c r="W2">
-        <v>0.1057266777314806</v>
+        <v>0.1503886298982066</v>
       </c>
       <c r="X2">
-        <v>0.2069635545364273</v>
+        <v>0.156910228270007</v>
       </c>
       <c r="Y2">
-        <v>-0.1012368768049466</v>
+        <v>-0.006521598371800413</v>
       </c>
       <c r="Z2">
-        <v>0.1612331218180962</v>
+        <v>0.3357149940408746</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08107180266822825</v>
+        <v>0.06928813969026132</v>
       </c>
       <c r="AC2">
-        <v>-0.08107180266822825</v>
+        <v>-0.06928813969026132</v>
       </c>
       <c r="AD2">
-        <v>425192.2</v>
+        <v>549777.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>425192.2</v>
+        <v>549777.8</v>
       </c>
       <c r="AG2">
-        <v>97079.79999999999</v>
+        <v>306080.7000000001</v>
       </c>
       <c r="AH2">
-        <v>0.8328915127150508</v>
+        <v>0.821590746404536</v>
       </c>
       <c r="AI2">
-        <v>0.7439891850124375</v>
+        <v>0.7686377003355132</v>
       </c>
       <c r="AJ2">
-        <v>0.5322681369315786</v>
+        <v>0.7194019256555467</v>
       </c>
       <c r="AK2">
-        <v>0.3988638847483142</v>
+        <v>0.6490735645419354</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Banco Bilbao Vizcaya Argentaria, S.A. (BME:BBVA)</t>
+          <t>Banco Santander, S.A. (BME:SAN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00282</v>
+        <v>0.0227</v>
       </c>
       <c r="E3">
-        <v>0.0842</v>
+        <v>0.0745</v>
       </c>
       <c r="F3">
-        <v>0.0673</v>
+        <v>0.08439999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>6063.9</v>
+        <v>11041.5</v>
       </c>
       <c r="L3">
-        <v>0.2892681833143315</v>
+        <v>0.2363284176280473</v>
       </c>
       <c r="M3">
-        <v>2035.8422</v>
+        <v>2366.567</v>
       </c>
       <c r="N3">
-        <v>0.05696527814697397</v>
+        <v>0.03566626125983564</v>
       </c>
       <c r="O3">
-        <v>0.3357314929335906</v>
+        <v>0.2143338314540597</v>
       </c>
       <c r="P3">
-        <v>2035.8422</v>
+        <v>2366.567</v>
       </c>
       <c r="Q3">
-        <v>0.05696527814697397</v>
+        <v>0.03566626125983564</v>
       </c>
       <c r="R3">
-        <v>0.3357314929335906</v>
+        <v>0.2143338314540597</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>86366</v>
+        <v>229738.6</v>
       </c>
       <c r="V3">
-        <v>2.416623062652672</v>
+        <v>3.462364230156541</v>
       </c>
       <c r="W3">
-        <v>0.1164229309341827</v>
+        <v>0.1237049991765324</v>
       </c>
       <c r="X3">
-        <v>0.1206119787453681</v>
+        <v>0.1884717324426361</v>
       </c>
       <c r="Y3">
-        <v>-0.004189047811185356</v>
+        <v>-0.06476673326610369</v>
       </c>
       <c r="Z3">
-        <v>0.1285951512348273</v>
+        <v>0.2278048604481301</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.08085456885908493</v>
+        <v>0.06906847030402774</v>
       </c>
       <c r="AC3">
-        <v>-0.08085456885908493</v>
+        <v>-0.06906847030402774</v>
       </c>
       <c r="AD3">
-        <v>53746.8</v>
+        <v>396398.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>53746.8</v>
+        <v>396398.2</v>
       </c>
       <c r="AG3">
-        <v>-32619.2</v>
+        <v>166659.6</v>
       </c>
       <c r="AH3">
-        <v>0.6006228969962597</v>
+        <v>0.8566117480383091</v>
       </c>
       <c r="AI3">
-        <v>0.5234704014648305</v>
+        <v>0.7844700350480005</v>
       </c>
       <c r="AJ3">
-        <v>-10.45788849347566</v>
+        <v>0.7152382681287329</v>
       </c>
       <c r="AK3">
-        <v>-2.000196222712779</v>
+        <v>0.604784873737337</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Banco Santander, S.A. (BME:SAN)</t>
+          <t>Banco Bilbao Vizcaya Argentaria, S.A. (BME:BBVA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0161</v>
+        <v>0.0388</v>
       </c>
       <c r="E4">
-        <v>0.07519999999999999</v>
+        <v>0.115</v>
       </c>
       <c r="F4">
-        <v>0.06</v>
+        <v>0.07719999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>9404.799999999999</v>
+        <v>8029.2</v>
       </c>
       <c r="L4">
-        <v>0.2332447125114083</v>
+        <v>0.3040960478724412</v>
       </c>
       <c r="M4">
-        <v>1787.4756</v>
+        <v>3671.4</v>
       </c>
       <c r="N4">
-        <v>0.03605904282359776</v>
+        <v>0.06923029056206005</v>
       </c>
       <c r="O4">
-        <v>0.190059926845866</v>
+        <v>0.4572560155432671</v>
       </c>
       <c r="P4">
-        <v>1787.4756</v>
+        <v>2729.7</v>
       </c>
       <c r="Q4">
-        <v>0.03605904282359776</v>
+        <v>0.05147298691160193</v>
       </c>
       <c r="R4">
-        <v>0.190059926845866</v>
+        <v>0.3399716036466895</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>941.6999999999998</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.2564961595031868</v>
       </c>
       <c r="U4">
-        <v>241746.4</v>
+        <v>13958.5</v>
       </c>
       <c r="V4">
-        <v>4.876790368523404</v>
+        <v>0.2632104948549641</v>
       </c>
       <c r="W4">
-        <v>0.09503042452877851</v>
+        <v>0.1770722606198808</v>
       </c>
       <c r="X4">
-        <v>0.2933151303274865</v>
+        <v>0.125348724097378</v>
       </c>
       <c r="Y4">
-        <v>-0.1982847057987079</v>
+        <v>0.05172353652250286</v>
       </c>
       <c r="Z4">
-        <v>0.1857419247848758</v>
+        <v>2.074931237721021</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.08128903647737157</v>
+        <v>0.06950780907649488</v>
       </c>
       <c r="AC4">
-        <v>-0.08128903647737157</v>
+        <v>-0.06950780907649488</v>
       </c>
       <c r="AD4">
-        <v>371445.4</v>
+        <v>153379.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>371445.4</v>
+        <v>153379.6</v>
       </c>
       <c r="AG4">
-        <v>129699</v>
+        <v>139421.1</v>
       </c>
       <c r="AH4">
-        <v>0.8822591624740331</v>
+        <v>0.7430775349992952</v>
       </c>
       <c r="AI4">
-        <v>0.7922829891994783</v>
+        <v>0.7305335032740256</v>
       </c>
       <c r="AJ4">
-        <v>0.723484937228691</v>
+        <v>0.7244430842263663</v>
       </c>
       <c r="AK4">
-        <v>0.5711529010563547</v>
+        <v>0.7113426678251872</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/spain/spain_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03075</v>
+        <v>0.077</v>
       </c>
       <c r="E2">
-        <v>0.09475</v>
+        <v>0.153</v>
       </c>
       <c r="F2">
-        <v>0.08079999999999998</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>19070.7</v>
+        <v>33255.9</v>
       </c>
       <c r="L2">
-        <v>0.260797680667902</v>
+        <v>0.2995673483579866</v>
       </c>
       <c r="M2">
-        <v>6037.967</v>
+        <v>14843.174</v>
       </c>
       <c r="N2">
-        <v>0.05057567630050056</v>
+        <v>0.0810469086997592</v>
       </c>
       <c r="O2">
-        <v>0.3166096157980567</v>
+        <v>0.4463320493506415</v>
       </c>
       <c r="P2">
-        <v>5096.267</v>
+        <v>11977.874</v>
       </c>
       <c r="Q2">
-        <v>0.04268773746741628</v>
+        <v>0.06540175709691334</v>
       </c>
       <c r="R2">
-        <v>0.2672302013035704</v>
+        <v>0.3601729016505342</v>
       </c>
       <c r="S2">
-        <v>941.6999999999998</v>
+        <v>2865.3</v>
       </c>
       <c r="T2">
-        <v>0.1559630915505169</v>
+        <v>0.1930382275381263</v>
       </c>
       <c r="U2">
-        <v>243697.1</v>
+        <v>323478</v>
       </c>
       <c r="V2">
-        <v>2.041274098545208</v>
+        <v>1.766259152683968</v>
       </c>
       <c r="W2">
-        <v>0.1503886298982066</v>
+        <v>0.1613514519034402</v>
       </c>
       <c r="X2">
-        <v>0.156910228270007</v>
+        <v>0.1254280904990235</v>
       </c>
       <c r="Y2">
-        <v>-0.006521598371800413</v>
+        <v>0.03592336140441668</v>
       </c>
       <c r="Z2">
-        <v>0.3357149940408746</v>
+        <v>0.2183424141258346</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06928813969026132</v>
+        <v>0.07157439822755751</v>
       </c>
       <c r="AC2">
-        <v>-0.06928813969026132</v>
+        <v>-0.07157439822755751</v>
       </c>
       <c r="AD2">
-        <v>549777.8</v>
+        <v>699952.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>549777.8</v>
+        <v>699952.6</v>
       </c>
       <c r="AG2">
-        <v>306080.7000000001</v>
+        <v>376474.6</v>
       </c>
       <c r="AH2">
-        <v>0.821590746404536</v>
+        <v>0.7926124872550605</v>
       </c>
       <c r="AI2">
-        <v>0.7686377003355132</v>
+        <v>0.7411425613313177</v>
       </c>
       <c r="AJ2">
-        <v>0.7194019256555467</v>
+        <v>0.6727354536383416</v>
       </c>
       <c r="AK2">
-        <v>0.6490735645419354</v>
+        <v>0.6062923054302494</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0227</v>
+        <v>0.0356</v>
       </c>
       <c r="E3">
-        <v>0.0745</v>
+        <v>0.161</v>
       </c>
       <c r="F3">
-        <v>0.08439999999999999</v>
+        <v>0.07629999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>11041.5</v>
+        <v>13653.8</v>
       </c>
       <c r="L3">
-        <v>0.2363284176280473</v>
+        <v>0.2561621270735853</v>
       </c>
       <c r="M3">
-        <v>2366.567</v>
+        <v>3285.7055</v>
       </c>
       <c r="N3">
-        <v>0.03566626125983564</v>
+        <v>0.04694837502053997</v>
       </c>
       <c r="O3">
-        <v>0.2143338314540597</v>
+        <v>0.240644033162929</v>
       </c>
       <c r="P3">
-        <v>2366.567</v>
+        <v>3285.7055</v>
       </c>
       <c r="Q3">
-        <v>0.03566626125983564</v>
+        <v>0.04694837502053997</v>
       </c>
       <c r="R3">
-        <v>0.2143338314540597</v>
+        <v>0.240644033162929</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>229738.6</v>
+        <v>188910.3</v>
       </c>
       <c r="V3">
-        <v>3.462364230156541</v>
+        <v>2.69927770752513</v>
       </c>
       <c r="W3">
-        <v>0.1237049991765324</v>
+        <v>0.1369496707101547</v>
       </c>
       <c r="X3">
-        <v>0.1884717324426361</v>
+        <v>0.1861506379601655</v>
       </c>
       <c r="Y3">
-        <v>-0.06476673326610369</v>
+        <v>-0.0492009672500108</v>
       </c>
       <c r="Z3">
-        <v>0.2278048604481301</v>
+        <v>0.2119636625086294</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06906847030402774</v>
+        <v>0.07111125451244261</v>
       </c>
       <c r="AC3">
-        <v>-0.06906847030402774</v>
+        <v>-0.07111125451244261</v>
       </c>
       <c r="AD3">
-        <v>396398.2</v>
+        <v>421235.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>396398.2</v>
+        <v>421235.8</v>
       </c>
       <c r="AG3">
-        <v>166659.6</v>
+        <v>232325.5</v>
       </c>
       <c r="AH3">
-        <v>0.8566117480383091</v>
+        <v>0.8575275542815427</v>
       </c>
       <c r="AI3">
-        <v>0.7844700350480005</v>
+        <v>0.7823625303227937</v>
       </c>
       <c r="AJ3">
-        <v>0.7152382681287329</v>
+        <v>0.7684983344965945</v>
       </c>
       <c r="AK3">
-        <v>0.604784873737337</v>
+        <v>0.6647276375031187</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,120 +829,495 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>CaixaBank, S.A. (BME:CABK)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.126</v>
+      </c>
+      <c r="E4">
+        <v>0.295</v>
+      </c>
+      <c r="F4">
+        <v>0.0473</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>6028.3</v>
+      </c>
+      <c r="L4">
+        <v>0.3849145031734073</v>
+      </c>
+      <c r="M4">
+        <v>4355.1675</v>
+      </c>
+      <c r="N4">
+        <v>0.1112365684774585</v>
+      </c>
+      <c r="O4">
+        <v>0.7224536768243119</v>
+      </c>
+      <c r="P4">
+        <v>4355.1675</v>
+      </c>
+      <c r="Q4">
+        <v>0.1112365684774585</v>
+      </c>
+      <c r="R4">
+        <v>0.7224536768243119</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>69614.10000000001</v>
+      </c>
+      <c r="V4">
+        <v>1.778033474406357</v>
+      </c>
+      <c r="W4">
+        <v>0.1613514519034402</v>
+      </c>
+      <c r="X4">
+        <v>0.1023308540940033</v>
+      </c>
+      <c r="Y4">
+        <v>0.05902059780943686</v>
+      </c>
+      <c r="Z4">
+        <v>0.2741740937395509</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.07152220867552006</v>
+      </c>
+      <c r="AC4">
+        <v>-0.07152220867552006</v>
+      </c>
+      <c r="AD4">
+        <v>63740.8</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>63740.8</v>
+      </c>
+      <c r="AG4">
+        <v>-5873.300000000003</v>
+      </c>
+      <c r="AH4">
+        <v>0.6194856603601213</v>
+      </c>
+      <c r="AI4">
+        <v>0.6069263385014421</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.1764866732774423</v>
+      </c>
+      <c r="AK4">
+        <v>-0.1658740065860451</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Banco Bilbao Vizcaya Argentaria, S.A. (BME:BBVA)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.0388</v>
-      </c>
-      <c r="E4">
-        <v>0.115</v>
-      </c>
-      <c r="F4">
-        <v>0.07719999999999999</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>8029.2</v>
-      </c>
-      <c r="L4">
-        <v>0.3040960478724412</v>
-      </c>
-      <c r="M4">
-        <v>3671.4</v>
-      </c>
-      <c r="N4">
-        <v>0.06923029056206005</v>
-      </c>
-      <c r="O4">
-        <v>0.4572560155432671</v>
-      </c>
-      <c r="P4">
-        <v>2729.7</v>
-      </c>
-      <c r="Q4">
-        <v>0.05147298691160193</v>
-      </c>
-      <c r="R4">
-        <v>0.3399716036466895</v>
-      </c>
-      <c r="S4">
-        <v>941.6999999999998</v>
-      </c>
-      <c r="T4">
-        <v>0.2564961595031868</v>
-      </c>
-      <c r="U4">
-        <v>13958.5</v>
-      </c>
-      <c r="V4">
-        <v>0.2632104948549641</v>
-      </c>
-      <c r="W4">
-        <v>0.1770722606198808</v>
-      </c>
-      <c r="X4">
-        <v>0.125348724097378</v>
-      </c>
-      <c r="Y4">
-        <v>0.05172353652250286</v>
-      </c>
-      <c r="Z4">
-        <v>2.074931237721021</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.06950780907649488</v>
-      </c>
-      <c r="AC4">
-        <v>-0.06950780907649488</v>
-      </c>
-      <c r="AD4">
-        <v>153379.6</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>153379.6</v>
-      </c>
-      <c r="AG4">
-        <v>139421.1</v>
-      </c>
-      <c r="AH4">
-        <v>0.7430775349992952</v>
-      </c>
-      <c r="AI4">
-        <v>0.7305335032740256</v>
-      </c>
-      <c r="AJ4">
-        <v>0.7244430842263663</v>
-      </c>
-      <c r="AK4">
-        <v>0.7113426678251872</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="D5">
+        <v>0.07980000000000001</v>
+      </c>
+      <c r="E5">
+        <v>0.153</v>
+      </c>
+      <c r="F5">
+        <v>0.0553</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>10796.3</v>
+      </c>
+      <c r="L5">
+        <v>0.3244499740050548</v>
+      </c>
+      <c r="M5">
+        <v>6429.9</v>
+      </c>
+      <c r="N5">
+        <v>0.1140099684916229</v>
+      </c>
+      <c r="O5">
+        <v>0.5955651473189889</v>
+      </c>
+      <c r="P5">
+        <v>3564.6</v>
+      </c>
+      <c r="Q5">
+        <v>0.06320470515641595</v>
+      </c>
+      <c r="R5">
+        <v>0.3301686688958254</v>
+      </c>
+      <c r="S5">
+        <v>2865.3</v>
+      </c>
+      <c r="T5">
+        <v>0.4456212382774227</v>
+      </c>
+      <c r="U5">
+        <v>17205</v>
+      </c>
+      <c r="V5">
+        <v>0.3050656321091109</v>
+      </c>
+      <c r="W5">
+        <v>0.2050322276789614</v>
+      </c>
+      <c r="X5">
+        <v>0.1254280904990235</v>
+      </c>
+      <c r="Y5">
+        <v>0.07960413717993792</v>
+      </c>
+      <c r="Z5">
+        <v>0.1740069653614458</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.07157439822755751</v>
+      </c>
+      <c r="AC5">
+        <v>-0.07157439822755751</v>
+      </c>
+      <c r="AD5">
+        <v>160054.7</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>160054.7</v>
+      </c>
+      <c r="AG5">
+        <v>142849.7</v>
+      </c>
+      <c r="AH5">
+        <v>0.7394452544762729</v>
+      </c>
+      <c r="AI5">
+        <v>0.716532683540915</v>
+      </c>
+      <c r="AJ5">
+        <v>0.7169463691872516</v>
+      </c>
+      <c r="AK5">
+        <v>0.6928770537166372</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bankinter, S.A. (BME:BKT)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.077</v>
+      </c>
+      <c r="E6">
+        <v>0.0946</v>
+      </c>
+      <c r="F6">
+        <v>0.03759999999999999</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>993.9</v>
+      </c>
+      <c r="L6">
+        <v>0.3656732891832229</v>
+      </c>
+      <c r="M6">
+        <v>107.832</v>
+      </c>
+      <c r="N6">
+        <v>0.01517051209904333</v>
+      </c>
+      <c r="O6">
+        <v>0.108493812254754</v>
+      </c>
+      <c r="P6">
+        <v>107.832</v>
+      </c>
+      <c r="Q6">
+        <v>0.01517051209904333</v>
+      </c>
+      <c r="R6">
+        <v>0.108493812254754</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>14384.8</v>
+      </c>
+      <c r="V6">
+        <v>2.023747889701744</v>
+      </c>
+      <c r="W6">
+        <v>0.1774251133564211</v>
+      </c>
+      <c r="X6">
+        <v>0.09964097362233607</v>
+      </c>
+      <c r="Y6">
+        <v>0.07778413973408507</v>
+      </c>
+      <c r="Z6">
+        <v>1.564586691227263</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.07196127511804606</v>
+      </c>
+      <c r="AC6">
+        <v>-0.07196127511804606</v>
+      </c>
+      <c r="AD6">
+        <v>10570.4</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>10570.4</v>
+      </c>
+      <c r="AG6">
+        <v>-3814.4</v>
+      </c>
+      <c r="AH6">
+        <v>0.597927414245633</v>
+      </c>
+      <c r="AI6">
+        <v>0.6154849453537594</v>
+      </c>
+      <c r="AJ6">
+        <v>-1.15812484819043</v>
+      </c>
+      <c r="AK6">
+        <v>-1.367511562040655</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Banco de Sabadell, S.A. (BME:SAB)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0399</v>
+      </c>
+      <c r="E7">
+        <v>0.131</v>
+      </c>
+      <c r="F7">
+        <v>0.05309999999999999</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1783.6</v>
+      </c>
+      <c r="L7">
+        <v>0.2944886570022785</v>
+      </c>
+      <c r="M7">
+        <v>664.569</v>
+      </c>
+      <c r="N7">
+        <v>0.06329529977617981</v>
+      </c>
+      <c r="O7">
+        <v>0.3725997981610226</v>
+      </c>
+      <c r="P7">
+        <v>664.569</v>
+      </c>
+      <c r="Q7">
+        <v>0.06329529977617981</v>
+      </c>
+      <c r="R7">
+        <v>0.3725997981610226</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>33363.8</v>
+      </c>
+      <c r="V7">
+        <v>3.177656078860899</v>
+      </c>
+      <c r="W7">
+        <v>0.122609472743521</v>
+      </c>
+      <c r="X7">
+        <v>0.1518886752161084</v>
+      </c>
+      <c r="Y7">
+        <v>-0.02927920247258736</v>
+      </c>
+      <c r="Z7">
+        <v>0.8803581551521137</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.07287798811509663</v>
+      </c>
+      <c r="AC7">
+        <v>-0.07287798811509663</v>
+      </c>
+      <c r="AD7">
+        <v>44350.9</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>44350.9</v>
+      </c>
+      <c r="AG7">
+        <v>10987.1</v>
+      </c>
+      <c r="AH7">
+        <v>0.8085793357933579</v>
+      </c>
+      <c r="AI7">
+        <v>0.7338211035055585</v>
+      </c>
+      <c r="AJ7">
+        <v>0.5113466067223292</v>
+      </c>
+      <c r="AK7">
+        <v>0.4058098949195737</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/spain/spain_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.077</v>
+        <v>0.0784</v>
       </c>
       <c r="E2">
-        <v>0.153</v>
+        <v>0.157</v>
       </c>
       <c r="F2">
-        <v>0.05309999999999999</v>
+        <v>0.0542</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>33255.9</v>
+        <v>33738.5</v>
       </c>
       <c r="L2">
-        <v>0.2995673483579866</v>
+        <v>0.2990784357874693</v>
       </c>
       <c r="M2">
         <v>14843.174</v>
       </c>
       <c r="N2">
-        <v>0.0810469086997592</v>
+        <v>0.0795939538689726</v>
       </c>
       <c r="O2">
-        <v>0.4463320493506415</v>
+        <v>0.439947656238422</v>
       </c>
       <c r="P2">
         <v>11977.874</v>
       </c>
       <c r="Q2">
-        <v>0.06540175709691334</v>
+        <v>0.06422927809135474</v>
       </c>
       <c r="R2">
-        <v>0.3601729016505342</v>
+        <v>0.3550209404686041</v>
       </c>
       <c r="S2">
         <v>2865.3</v>
@@ -639,55 +639,55 @@
         <v>0.1930382275381263</v>
       </c>
       <c r="U2">
-        <v>323478</v>
+        <v>331036.6</v>
       </c>
       <c r="V2">
-        <v>1.766259152683968</v>
+        <v>1.775126524107414</v>
       </c>
       <c r="W2">
-        <v>0.1613514519034402</v>
+        <v>0.1491505613067975</v>
       </c>
       <c r="X2">
-        <v>0.1254280904990235</v>
+        <v>0.1158761138137601</v>
       </c>
       <c r="Y2">
-        <v>0.03592336140441668</v>
+        <v>0.0332744474930374</v>
       </c>
       <c r="Z2">
-        <v>0.2183424141258346</v>
+        <v>0.2195919818156795</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07157439822755751</v>
+        <v>0.07176210138642219</v>
       </c>
       <c r="AC2">
-        <v>-0.07157439822755751</v>
+        <v>-0.07176210138642219</v>
       </c>
       <c r="AD2">
-        <v>699952.6</v>
+        <v>706101.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>699952.6</v>
+        <v>706101.4</v>
       </c>
       <c r="AG2">
-        <v>376474.6</v>
+        <v>375064.8</v>
       </c>
       <c r="AH2">
-        <v>0.7926124872550605</v>
+        <v>0.7910723832596375</v>
       </c>
       <c r="AI2">
-        <v>0.7411425613313177</v>
+        <v>0.7368798392538587</v>
       </c>
       <c r="AJ2">
-        <v>0.6727354536383416</v>
+        <v>0.6679087028604704</v>
       </c>
       <c r="AK2">
-        <v>0.6062923054302494</v>
+        <v>0.5980036824284896</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -773,10 +773,10 @@
         <v>0.1369496707101547</v>
       </c>
       <c r="X3">
-        <v>0.1861506379601655</v>
+        <v>0.1861126644992457</v>
       </c>
       <c r="Y3">
-        <v>-0.0492009672500108</v>
+        <v>-0.04916299378909098</v>
       </c>
       <c r="Z3">
         <v>0.2119636625086294</v>
@@ -785,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07111125451244261</v>
+        <v>0.07110584434059297</v>
       </c>
       <c r="AC3">
-        <v>-0.07111125451244261</v>
+        <v>-0.07110584434059297</v>
       </c>
       <c r="AD3">
         <v>421235.8</v>
@@ -898,10 +898,10 @@
         <v>0.1613514519034402</v>
       </c>
       <c r="X4">
-        <v>0.1023308540940033</v>
+        <v>0.1023155590286591</v>
       </c>
       <c r="Y4">
-        <v>0.05902059780943686</v>
+        <v>0.05903589287478107</v>
       </c>
       <c r="Z4">
         <v>0.2741740937395509</v>
@@ -910,10 +910,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07152220867552006</v>
+        <v>0.07151638868383087</v>
       </c>
       <c r="AC4">
-        <v>-0.07152220867552006</v>
+        <v>-0.07151638868383087</v>
       </c>
       <c r="AD4">
         <v>63740.8</v>
@@ -1023,10 +1023,10 @@
         <v>0.2050322276789614</v>
       </c>
       <c r="X5">
-        <v>0.1254280904990235</v>
+        <v>0.1254065462137489</v>
       </c>
       <c r="Y5">
-        <v>0.07960413717993792</v>
+        <v>0.07962568146521251</v>
       </c>
       <c r="Z5">
         <v>0.1740069653614458</v>
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07157439822755751</v>
+        <v>0.07156878476179029</v>
       </c>
       <c r="AC5">
-        <v>-0.07157439822755751</v>
+        <v>-0.07156878476179029</v>
       </c>
       <c r="AD5">
         <v>160054.7</v>
@@ -1148,10 +1148,10 @@
         <v>0.1774251133564211</v>
       </c>
       <c r="X6">
-        <v>0.09964097362233607</v>
+        <v>0.09962640633473804</v>
       </c>
       <c r="Y6">
-        <v>0.07778413973408507</v>
+        <v>0.07779870702168309</v>
       </c>
       <c r="Z6">
         <v>1.564586691227263</v>
@@ -1160,10 +1160,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.07196127511804606</v>
+        <v>0.0719554180110541</v>
       </c>
       <c r="AC6">
-        <v>-0.07196127511804606</v>
+        <v>-0.0719554180110541</v>
       </c>
       <c r="AD6">
         <v>10570.4</v>
@@ -1204,120 +1204,242 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Unicaja Banco, S.A. (BME:UNI)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0953</v>
+      </c>
+      <c r="E7">
+        <v>0.206</v>
+      </c>
+      <c r="F7">
+        <v>0.235</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>482.6</v>
+      </c>
+      <c r="L7">
+        <v>0.2688429613949084</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>-0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>-0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>7558.6</v>
+      </c>
+      <c r="V7">
+        <v>2.260887772194305</v>
+      </c>
+      <c r="W7">
+        <v>0.06972980783123826</v>
+      </c>
+      <c r="X7">
+        <v>0.1063456814137712</v>
+      </c>
+      <c r="Y7">
+        <v>-0.03661587358253295</v>
+      </c>
+      <c r="Z7">
+        <v>0.339884502508757</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.07201459114746092</v>
+      </c>
+      <c r="AC7">
+        <v>-0.07201459114746092</v>
+      </c>
+      <c r="AD7">
+        <v>6148.8</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>6148.8</v>
+      </c>
+      <c r="AG7">
+        <v>-1409.8</v>
+      </c>
+      <c r="AH7">
+        <v>0.6477876106194691</v>
+      </c>
+      <c r="AI7">
+        <v>0.4453167435561317</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.7291817523533674</v>
+      </c>
+      <c r="AK7">
+        <v>-0.2256004864700517</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Banco de Sabadell, S.A. (BME:SAB)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>0.0399</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>0.131</v>
       </c>
-      <c r="F7">
+      <c r="F8">
         <v>0.05309999999999999</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>1783.6</v>
       </c>
-      <c r="L7">
+      <c r="L8">
         <v>0.2944886570022785</v>
       </c>
-      <c r="M7">
+      <c r="M8">
         <v>664.569</v>
       </c>
-      <c r="N7">
+      <c r="N8">
         <v>0.06329529977617981</v>
       </c>
-      <c r="O7">
+      <c r="O8">
         <v>0.3725997981610226</v>
       </c>
-      <c r="P7">
+      <c r="P8">
         <v>664.569</v>
       </c>
-      <c r="Q7">
+      <c r="Q8">
         <v>0.06329529977617981</v>
       </c>
-      <c r="R7">
+      <c r="R8">
         <v>0.3725997981610226</v>
       </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
         <v>33363.8</v>
       </c>
-      <c r="V7">
+      <c r="V8">
         <v>3.177656078860899</v>
       </c>
-      <c r="W7">
+      <c r="W8">
         <v>0.122609472743521</v>
       </c>
-      <c r="X7">
-        <v>0.1518886752161084</v>
-      </c>
-      <c r="Y7">
-        <v>-0.02927920247258736</v>
-      </c>
-      <c r="Z7">
+      <c r="X8">
+        <v>0.1518599717187755</v>
+      </c>
+      <c r="Y8">
+        <v>-0.0292504989752545</v>
+      </c>
+      <c r="Z8">
         <v>0.8803581551521137</v>
       </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.07287798811509663</v>
-      </c>
-      <c r="AC7">
-        <v>-0.07287798811509663</v>
-      </c>
-      <c r="AD7">
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.07287249367257212</v>
+      </c>
+      <c r="AC8">
+        <v>-0.07287249367257212</v>
+      </c>
+      <c r="AD8">
         <v>44350.9</v>
       </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
         <v>44350.9</v>
       </c>
-      <c r="AG7">
+      <c r="AG8">
         <v>10987.1</v>
       </c>
-      <c r="AH7">
+      <c r="AH8">
         <v>0.8085793357933579</v>
       </c>
-      <c r="AI7">
+      <c r="AI8">
         <v>0.7338211035055585</v>
       </c>
-      <c r="AJ7">
+      <c r="AJ8">
         <v>0.5113466067223292</v>
       </c>
-      <c r="AK7">
+      <c r="AK8">
         <v>0.4058098949195737</v>
       </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
         <v>0</v>
       </c>
     </row>
